--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/17.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/17.xlsx
@@ -426,13 +426,13 @@
         <v>-8.128861455704328</v>
       </c>
       <c r="E2">
-        <v>-6.798296696664596</v>
+        <v>-5.017673546004565</v>
       </c>
       <c r="F2">
-        <v>-5.754202123647898</v>
+        <v>-6.387923895974589</v>
       </c>
       <c r="G2">
-        <v>-5.515317050365503</v>
+        <v>-6.77157307669828</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.431276062895494</v>
       </c>
       <c r="E3">
-        <v>-6.304267353271806</v>
+        <v>-5.309588037487011</v>
       </c>
       <c r="F3">
-        <v>-5.812544039827066</v>
+        <v>-6.16818453176877</v>
       </c>
       <c r="G3">
-        <v>-5.270965684111897</v>
+        <v>-6.268628377281122</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.10426151645367</v>
       </c>
       <c r="E4">
-        <v>-7.183642663873297</v>
+        <v>-6.268709775363578</v>
       </c>
       <c r="F4">
-        <v>-5.938903203450103</v>
+        <v>-6.138483418541393</v>
       </c>
       <c r="G4">
-        <v>-5.451502974550512</v>
+        <v>-6.709920787120432</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.89134624701954</v>
       </c>
       <c r="E5">
-        <v>-8.197984613799395</v>
+        <v>-7.107519015804359</v>
       </c>
       <c r="F5">
-        <v>-5.488561264918152</v>
+        <v>-5.812194468783085</v>
       </c>
       <c r="G5">
-        <v>-5.478771938157489</v>
+        <v>-7.038485810802019</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.73558025038833</v>
       </c>
       <c r="E6">
-        <v>-7.859535523414128</v>
+        <v>-8.127761567362452</v>
       </c>
       <c r="F6">
-        <v>-5.699124803403161</v>
+        <v>-5.909131678993488</v>
       </c>
       <c r="G6">
-        <v>-6.18210726961227</v>
+        <v>-7.582981167282569</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.49340358241852</v>
       </c>
       <c r="E7">
-        <v>-9.629344678143843</v>
+        <v>-8.589847055105135</v>
       </c>
       <c r="F7">
-        <v>-5.915756961481079</v>
+        <v>-5.935332939944037</v>
       </c>
       <c r="G7">
-        <v>-5.257468589948288</v>
+        <v>-6.969752264315671</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.06055759325209</v>
       </c>
       <c r="E8">
-        <v>-10.13606280570612</v>
+        <v>-9.144023590267803</v>
       </c>
       <c r="F8">
-        <v>-5.776529938622955</v>
+        <v>-5.994029397371604</v>
       </c>
       <c r="G8">
-        <v>-6.424276986355497</v>
+        <v>-6.935445080892204</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.31359568494036</v>
       </c>
       <c r="E9">
-        <v>-11.03114739264023</v>
+        <v>-10.51437605278091</v>
       </c>
       <c r="F9">
-        <v>-5.616848039487503</v>
+        <v>-5.657418989774414</v>
       </c>
       <c r="G9">
-        <v>-5.200441132488803</v>
+        <v>-6.647490519340857</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.15992641678711</v>
       </c>
       <c r="E10">
-        <v>-11.74994301492973</v>
+        <v>-9.985971063195898</v>
       </c>
       <c r="F10">
-        <v>-5.666884744086204</v>
+        <v>-5.664904117626111</v>
       </c>
       <c r="G10">
-        <v>-5.952686463740776</v>
+        <v>-6.280966780505986</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.51895685225786</v>
       </c>
       <c r="E11">
-        <v>-12.69601369071619</v>
+        <v>-11.65083283279785</v>
       </c>
       <c r="F11">
-        <v>-5.101065076134391</v>
+        <v>-5.385278760402303</v>
       </c>
       <c r="G11">
-        <v>-5.054118330198555</v>
+        <v>-6.911579358099598</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.3478352784964</v>
       </c>
       <c r="E12">
-        <v>-12.35996469155498</v>
+        <v>-11.69608134508249</v>
       </c>
       <c r="F12">
-        <v>-5.066197435415754</v>
+        <v>-5.395239878420968</v>
       </c>
       <c r="G12">
-        <v>-4.965663863934768</v>
+        <v>-6.100472527159382</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.63594220604431</v>
       </c>
       <c r="E13">
-        <v>-12.53215085874863</v>
+        <v>-12.1887023330589</v>
       </c>
       <c r="F13">
-        <v>-5.169799689749082</v>
+        <v>-5.187366877260251</v>
       </c>
       <c r="G13">
-        <v>-4.523656376258976</v>
+        <v>-5.679722052391249</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.41968510402712</v>
       </c>
       <c r="E14">
-        <v>-14.5627638885281</v>
+        <v>-12.9890286013825</v>
       </c>
       <c r="F14">
-        <v>-4.764316331180932</v>
+        <v>-5.167818234921586</v>
       </c>
       <c r="G14">
-        <v>-5.279543307604149</v>
+        <v>-5.74872044252074</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.77505985362766</v>
       </c>
       <c r="E15">
-        <v>-14.38598132021666</v>
+        <v>-13.71627435617031</v>
       </c>
       <c r="F15">
-        <v>-4.54155756779191</v>
+        <v>-4.983456785754528</v>
       </c>
       <c r="G15">
-        <v>-3.788003499249829</v>
+        <v>-5.23506612828404</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.81532801539885</v>
       </c>
       <c r="E16">
-        <v>-15.27002548752006</v>
+        <v>-14.63651008774301</v>
       </c>
       <c r="F16">
-        <v>-4.498436074271778</v>
+        <v>-4.959150001054182</v>
       </c>
       <c r="G16">
-        <v>-3.792184718265929</v>
+        <v>-4.849913949699691</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.67995561163411</v>
       </c>
       <c r="E17">
-        <v>-15.99802296899315</v>
+        <v>-14.70224994491236</v>
       </c>
       <c r="F17">
-        <v>-4.169063112672847</v>
+        <v>-4.724234117661673</v>
       </c>
       <c r="G17">
-        <v>-2.377836900250796</v>
+        <v>-3.925046842393499</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.51983034181683</v>
       </c>
       <c r="E18">
-        <v>-15.86579605644318</v>
+        <v>-16.31895139344274</v>
       </c>
       <c r="F18">
-        <v>-3.641703714865612</v>
+        <v>-4.197196954774126</v>
       </c>
       <c r="G18">
-        <v>-2.885479263788179</v>
+        <v>-3.460958015970768</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.485726269315741</v>
       </c>
       <c r="E19">
-        <v>-17.92842086898287</v>
+        <v>-16.03954001869547</v>
       </c>
       <c r="F19">
-        <v>-3.725324919076014</v>
+        <v>-3.900050798613708</v>
       </c>
       <c r="G19">
-        <v>-2.142188958219934</v>
+        <v>-3.679285183740164</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.703162292990786</v>
       </c>
       <c r="E20">
-        <v>-18.85342508368565</v>
+        <v>-16.57966017053833</v>
       </c>
       <c r="F20">
-        <v>-3.384372209553348</v>
+        <v>-3.952295930708273</v>
       </c>
       <c r="G20">
-        <v>-2.044478206628344</v>
+        <v>-3.619086223654056</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.261749116269526</v>
       </c>
       <c r="E21">
-        <v>-19.21758232101246</v>
+        <v>-17.47843999226269</v>
       </c>
       <c r="F21">
-        <v>-2.927824142439623</v>
+        <v>-3.518878366582918</v>
       </c>
       <c r="G21">
-        <v>-2.376151832571307</v>
+        <v>-3.014875246736133</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.207793862728709</v>
       </c>
       <c r="E22">
-        <v>-19.79273021930465</v>
+        <v>-17.32206725630382</v>
       </c>
       <c r="F22">
-        <v>-2.846779989219331</v>
+        <v>-3.415302620006479</v>
       </c>
       <c r="G22">
-        <v>-2.352312594143015</v>
+        <v>-3.335713457129061</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.552029360217304</v>
       </c>
       <c r="E23">
-        <v>-19.75393931095494</v>
+        <v>-17.96379730793079</v>
       </c>
       <c r="F23">
-        <v>-2.750401098638414</v>
+        <v>-3.44955312701003</v>
       </c>
       <c r="G23">
-        <v>-2.494940827611436</v>
+        <v>-3.229683304597283</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.275886189719568</v>
       </c>
       <c r="E24">
-        <v>-20.80788729455213</v>
+        <v>-19.15962691066229</v>
       </c>
       <c r="F24">
-        <v>-2.381637610301561</v>
+        <v>-2.88774689912478</v>
       </c>
       <c r="G24">
-        <v>-2.617265485287506</v>
+        <v>-2.776373614450419</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.332563318103078</v>
       </c>
       <c r="E25">
-        <v>-20.47057485114279</v>
+        <v>-19.26309801326355</v>
       </c>
       <c r="F25">
-        <v>-2.376255707285572</v>
+        <v>-2.792420863512822</v>
       </c>
       <c r="G25">
-        <v>-2.704587744976862</v>
+        <v>-3.39680957505631</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.658806819385408</v>
       </c>
       <c r="E26">
-        <v>-22.14532680797749</v>
+        <v>-19.32297802506698</v>
       </c>
       <c r="F26">
-        <v>-1.958219269095399</v>
+        <v>-2.843541901041788</v>
       </c>
       <c r="G26">
-        <v>-2.937067494926642</v>
+        <v>-3.079732144395995</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.183706959984175</v>
       </c>
       <c r="E27">
-        <v>-20.34529461772059</v>
+        <v>-19.46592836406711</v>
       </c>
       <c r="F27">
-        <v>-2.332507968008925</v>
+        <v>-2.907746173330569</v>
       </c>
       <c r="G27">
-        <v>-3.557887478815089</v>
+        <v>-3.395568120479084</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.842554592441878</v>
       </c>
       <c r="E28">
-        <v>-21.02323434751288</v>
+        <v>-19.60641974168107</v>
       </c>
       <c r="F28">
-        <v>-2.223078148996902</v>
+        <v>-2.782495365292478</v>
       </c>
       <c r="G28">
-        <v>-4.001662797808852</v>
+        <v>-3.667572473622222</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.5763088735827</v>
       </c>
       <c r="E29">
-        <v>-21.755973141272</v>
+        <v>-19.23260779776991</v>
       </c>
       <c r="F29">
-        <v>-2.344023103275241</v>
+        <v>-2.807850863124768</v>
       </c>
       <c r="G29">
-        <v>-3.274534575563329</v>
+        <v>-3.423174759731066</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.332286120042094</v>
       </c>
       <c r="E30">
-        <v>-21.7517254326528</v>
+        <v>-19.01148694044937</v>
       </c>
       <c r="F30">
-        <v>-2.168148278149864</v>
+        <v>-2.886833209879492</v>
       </c>
       <c r="G30">
-        <v>-3.23514901528262</v>
+        <v>-3.656435798428114</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.065335537680943</v>
       </c>
       <c r="E31">
-        <v>-21.13958443019196</v>
+        <v>-19.71057464385749</v>
       </c>
       <c r="F31">
-        <v>-2.372921528489304</v>
+        <v>-3.061490334922754</v>
       </c>
       <c r="G31">
-        <v>-3.729681618484489</v>
+        <v>-3.919478504796445</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.740814135581057</v>
       </c>
       <c r="E32">
-        <v>-21.1692459349422</v>
+        <v>-19.28885597341918</v>
       </c>
       <c r="F32">
-        <v>-2.75945432598361</v>
+        <v>-3.173299225115617</v>
       </c>
       <c r="G32">
-        <v>-3.504150703621639</v>
+        <v>-3.392214537847802</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.336540522557597</v>
       </c>
       <c r="E33">
-        <v>-20.29601123509511</v>
+        <v>-19.29161381408985</v>
       </c>
       <c r="F33">
-        <v>-2.605245450278454</v>
+        <v>-3.159824172574278</v>
       </c>
       <c r="G33">
-        <v>-2.412624112777458</v>
+        <v>-3.494010502634852</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.838451638737741</v>
       </c>
       <c r="E34">
-        <v>-20.28877020515684</v>
+        <v>-18.65838823664929</v>
       </c>
       <c r="F34">
-        <v>-2.784130562545604</v>
+        <v>-3.152412769421431</v>
       </c>
       <c r="G34">
-        <v>-2.706878642490038</v>
+        <v>-2.573705327081776</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.241132173758196</v>
       </c>
       <c r="E35">
-        <v>-19.61880511809205</v>
+        <v>-18.3148491414794</v>
       </c>
       <c r="F35">
-        <v>-2.606705862009589</v>
+        <v>-3.02042733439858</v>
       </c>
       <c r="G35">
-        <v>-2.892709495245947</v>
+        <v>-3.191837147992335</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.544553839539804</v>
       </c>
       <c r="E36">
-        <v>-19.54486872296882</v>
+        <v>-18.13670803096567</v>
       </c>
       <c r="F36">
-        <v>-2.425498835912392</v>
+        <v>-3.466967894919084</v>
       </c>
       <c r="G36">
-        <v>-2.041644379646729</v>
+        <v>-2.729704853983313</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.753115994737692</v>
       </c>
       <c r="E37">
-        <v>-19.24453579830611</v>
+        <v>-17.89064433881088</v>
       </c>
       <c r="F37">
-        <v>-2.672146058463347</v>
+        <v>-3.258597044949285</v>
       </c>
       <c r="G37">
-        <v>-2.504220286758013</v>
+        <v>-2.613809275744507</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.872324563437775</v>
       </c>
       <c r="E38">
-        <v>-19.51551062597709</v>
+        <v>-16.87703147320002</v>
       </c>
       <c r="F38">
-        <v>-2.691934927348825</v>
+        <v>-3.454631019189191</v>
       </c>
       <c r="G38">
-        <v>-2.059955007024437</v>
+        <v>-2.915740960562657</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.905702676340818</v>
       </c>
       <c r="E39">
-        <v>-19.36818578108555</v>
+        <v>-16.42149868734644</v>
       </c>
       <c r="F39">
-        <v>-2.78132736725453</v>
+        <v>-3.224166782219327</v>
       </c>
       <c r="G39">
-        <v>-2.557506827758122</v>
+        <v>-2.317051973604238</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.855146309968189</v>
       </c>
       <c r="E40">
-        <v>-19.37794011409807</v>
+        <v>-16.64275992736121</v>
       </c>
       <c r="F40">
-        <v>-2.622950146778487</v>
+        <v>-3.347948066484851</v>
       </c>
       <c r="G40">
-        <v>-0.8500995869700857</v>
+        <v>-2.545257809262818</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.720012110943781</v>
       </c>
       <c r="E41">
-        <v>-18.45350195864625</v>
+        <v>-16.85812056574399</v>
       </c>
       <c r="F41">
-        <v>-2.925913098841365</v>
+        <v>-3.100979437381609</v>
       </c>
       <c r="G41">
-        <v>-0.8356325029634706</v>
+        <v>-2.159652085939589</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.500171779901448</v>
       </c>
       <c r="E42">
-        <v>-17.19852142842656</v>
+        <v>-14.98280702358357</v>
       </c>
       <c r="F42">
-        <v>-2.726345309261116</v>
+        <v>-3.414812226504022</v>
       </c>
       <c r="G42">
-        <v>-1.319150921156184</v>
+        <v>-2.530777483074046</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.198811140521832</v>
       </c>
       <c r="E43">
-        <v>-17.8276034521501</v>
+        <v>-16.2450104698455</v>
       </c>
       <c r="F43">
-        <v>-2.487283447017596</v>
+        <v>-3.493256134446927</v>
       </c>
       <c r="G43">
-        <v>-1.190426978952703</v>
+        <v>-2.200557186622824</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.82207571585282</v>
       </c>
       <c r="E44">
-        <v>-17.42378131099011</v>
+        <v>-14.72845622399475</v>
       </c>
       <c r="F44">
-        <v>-2.936076338506312</v>
+        <v>-3.68989316015607</v>
       </c>
       <c r="G44">
-        <v>-0.4438790965738147</v>
+        <v>-1.663179503051707</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.381274165678292</v>
       </c>
       <c r="E45">
-        <v>-16.4174638170056</v>
+        <v>-14.860261988462</v>
       </c>
       <c r="F45">
-        <v>-2.644067716978055</v>
+        <v>-3.552118265355054</v>
       </c>
       <c r="G45">
-        <v>-1.136392254660719</v>
+        <v>-1.755262327226535</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.890910606717697</v>
       </c>
       <c r="E46">
-        <v>-16.14126313032977</v>
+        <v>-14.19609334812703</v>
       </c>
       <c r="F46">
-        <v>-3.213374811695655</v>
+        <v>-3.740903196453061</v>
       </c>
       <c r="G46">
-        <v>-1.025439320912045</v>
+        <v>-1.35092222669657</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.37077861802655</v>
       </c>
       <c r="E47">
-        <v>-16.807945073739</v>
+        <v>-14.34544694937401</v>
       </c>
       <c r="F47">
-        <v>-3.003990868392232</v>
+        <v>-3.63179064215631</v>
       </c>
       <c r="G47">
-        <v>-0.7231236128113393</v>
+        <v>-2.0221518875115</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.845750043521535</v>
       </c>
       <c r="E48">
-        <v>-15.65482350937384</v>
+        <v>-14.17918402618239</v>
       </c>
       <c r="F48">
-        <v>-2.829364392942874</v>
+        <v>-3.73346694227813</v>
       </c>
       <c r="G48">
-        <v>-0.94628748761361</v>
+        <v>-2.023731017733732</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.341714183920797</v>
       </c>
       <c r="E49">
-        <v>-14.45763083596602</v>
+        <v>-12.78418307964553</v>
       </c>
       <c r="F49">
-        <v>-2.985116517119446</v>
+        <v>-4.017252360598796</v>
       </c>
       <c r="G49">
-        <v>-1.284214734080256</v>
+        <v>-1.454697897716104</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.883929641318258</v>
       </c>
       <c r="E50">
-        <v>-13.37884417243677</v>
+        <v>-13.51231641533884</v>
       </c>
       <c r="F50">
-        <v>-3.262605514811432</v>
+        <v>-3.757370312053312</v>
       </c>
       <c r="G50">
-        <v>-1.147999027321403</v>
+        <v>-1.895040180985643</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.49319766233727</v>
       </c>
       <c r="E51">
-        <v>-14.55780068101569</v>
+        <v>-12.43280519596836</v>
       </c>
       <c r="F51">
-        <v>-2.927443921801738</v>
+        <v>-4.223228400407101</v>
       </c>
       <c r="G51">
-        <v>-1.237264577242312</v>
+        <v>-1.534462181939304</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.18755284698795</v>
       </c>
       <c r="E52">
-        <v>-14.7781381123329</v>
+        <v>-12.63384679953889</v>
       </c>
       <c r="F52">
-        <v>-3.31282777370836</v>
+        <v>-4.06639028656546</v>
       </c>
       <c r="G52">
-        <v>-0.8089296426437091</v>
+        <v>-1.523583729297259</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.978229729317442</v>
       </c>
       <c r="E53">
-        <v>-13.93134064374259</v>
+        <v>-12.12617769243499</v>
       </c>
       <c r="F53">
-        <v>-3.63007426489771</v>
+        <v>-4.198765054267626</v>
       </c>
       <c r="G53">
-        <v>-1.116144958142536</v>
+        <v>-1.208350272502317</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.871201333659499</v>
       </c>
       <c r="E54">
-        <v>-13.57512182135122</v>
+        <v>-11.42392458569551</v>
       </c>
       <c r="F54">
-        <v>-3.399114664220971</v>
+        <v>-3.934781758710883</v>
       </c>
       <c r="G54">
-        <v>-1.559304515665995</v>
+        <v>-1.825104906468539</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.870724422485743</v>
       </c>
       <c r="E55">
-        <v>-14.43982034769386</v>
+        <v>-10.31993696431357</v>
       </c>
       <c r="F55">
-        <v>-3.44435429319006</v>
+        <v>-4.281462628823906</v>
       </c>
       <c r="G55">
-        <v>-1.636042961266301</v>
+        <v>-2.063487359114839</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.976392332566896</v>
       </c>
       <c r="E56">
-        <v>-12.14349910551433</v>
+        <v>-10.46284654704763</v>
       </c>
       <c r="F56">
-        <v>-3.346484341284104</v>
+        <v>-4.240280343393729</v>
       </c>
       <c r="G56">
-        <v>-1.173255179240503</v>
+        <v>-1.888452195362494</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.185452637120066</v>
       </c>
       <c r="E57">
-        <v>-13.96838356112533</v>
+        <v>-9.483862922173424</v>
       </c>
       <c r="F57">
-        <v>-3.991177839860876</v>
+        <v>-4.54733957226345</v>
       </c>
       <c r="G57">
-        <v>-2.191254553657472</v>
+        <v>-1.523100389648525</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.488780571816025</v>
       </c>
       <c r="E58">
-        <v>-13.15738367956566</v>
+        <v>-10.07260982791065</v>
       </c>
       <c r="F58">
-        <v>-3.473666902105524</v>
+        <v>-4.43589847719743</v>
       </c>
       <c r="G58">
-        <v>-1.538338830765791</v>
+        <v>-2.269469502568293</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.869613535696257</v>
       </c>
       <c r="E59">
-        <v>-11.8106200381585</v>
+        <v>-10.52579233575425</v>
       </c>
       <c r="F59">
-        <v>-3.783229457266505</v>
+        <v>-4.310122484225964</v>
       </c>
       <c r="G59">
-        <v>-2.59212851300782</v>
+        <v>-1.454846872265371</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.302275991322499</v>
       </c>
       <c r="E60">
-        <v>-12.09009481154188</v>
+        <v>-10.05269359922491</v>
       </c>
       <c r="F60">
-        <v>-3.471880941985088</v>
+        <v>-4.604467930197518</v>
       </c>
       <c r="G60">
-        <v>-1.098205111865226</v>
+        <v>-1.824856615553094</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.756956354610168</v>
       </c>
       <c r="E61">
-        <v>-11.8851858911688</v>
+        <v>-9.422524741739529</v>
       </c>
       <c r="F61">
-        <v>-3.898783396487425</v>
+        <v>-4.562042265295738</v>
       </c>
       <c r="G61">
-        <v>-1.987321637892828</v>
+        <v>-2.079318387883634</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.205775698709935</v>
       </c>
       <c r="E62">
-        <v>-11.22723484564636</v>
+        <v>-9.949996865678965</v>
       </c>
       <c r="F62">
-        <v>-3.619070232318921</v>
+        <v>-4.446199225851242</v>
       </c>
       <c r="G62">
-        <v>-1.772669175672023</v>
+        <v>-2.386000705550639</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.622788453389772</v>
       </c>
       <c r="E63">
-        <v>-11.43747377992646</v>
+        <v>-9.063856014910014</v>
       </c>
       <c r="F63">
-        <v>-3.997292848028342</v>
+        <v>-4.425492525883462</v>
       </c>
       <c r="G63">
-        <v>-2.453863578560159</v>
+        <v>-1.960559187753359</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.984882868638201</v>
       </c>
       <c r="E64">
-        <v>-11.11138742358214</v>
+        <v>-8.819757680474559</v>
       </c>
       <c r="F64">
-        <v>-3.772736527375243</v>
+        <v>-4.571936285554775</v>
       </c>
       <c r="G64">
-        <v>-2.055340106542694</v>
+        <v>-2.41097877164444</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.272681048156311</v>
       </c>
       <c r="E65">
-        <v>-10.50564062642012</v>
+        <v>-9.829476058438827</v>
       </c>
       <c r="F65">
-        <v>-3.657583517977279</v>
+        <v>-4.810929393303864</v>
       </c>
       <c r="G65">
-        <v>-2.200560497168363</v>
+        <v>-2.507931408307536</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.479135786135148</v>
       </c>
       <c r="E66">
-        <v>-11.10920469911044</v>
+        <v>-9.272455641599342</v>
       </c>
       <c r="F66">
-        <v>-4.025604789121223</v>
+        <v>-4.278169868397779</v>
       </c>
       <c r="G66">
-        <v>-2.930903259132519</v>
+        <v>-2.182554439980267</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.605919987354413</v>
       </c>
       <c r="E67">
-        <v>-10.64741809065226</v>
+        <v>-8.687313401172224</v>
       </c>
       <c r="F67">
-        <v>-3.659853244660949</v>
+        <v>-4.45272924608751</v>
       </c>
       <c r="G67">
-        <v>-2.607330538124153</v>
+        <v>-2.024412990114822</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.656884812567741</v>
       </c>
       <c r="E68">
-        <v>-10.62106237192762</v>
+        <v>-8.760475427240147</v>
       </c>
       <c r="F68">
-        <v>-3.728848794007523</v>
+        <v>-4.507659116934548</v>
       </c>
       <c r="G68">
-        <v>-2.148707422386758</v>
+        <v>-2.039734194870569</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.638876547107172</v>
       </c>
       <c r="E69">
-        <v>-11.18033344034892</v>
+        <v>-8.430358729028992</v>
       </c>
       <c r="F69">
-        <v>-4.17155815529008</v>
+        <v>-4.670179002791992</v>
       </c>
       <c r="G69">
-        <v>-2.328228375344817</v>
+        <v>-1.761241172470459</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.559963629908156</v>
       </c>
       <c r="E70">
-        <v>-11.17796957691691</v>
+        <v>-8.438537153086845</v>
       </c>
       <c r="F70">
-        <v>-3.868435328318462</v>
+        <v>-4.430679762559793</v>
       </c>
       <c r="G70">
-        <v>-2.274309520146708</v>
+        <v>-1.977489317641192</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.43183233079416</v>
       </c>
       <c r="E71">
-        <v>-10.53975814959391</v>
+        <v>-9.751391581124567</v>
       </c>
       <c r="F71">
-        <v>-3.807102177447784</v>
+        <v>-4.857674165843839</v>
       </c>
       <c r="G71">
-        <v>-2.129320867708786</v>
+        <v>-2.114062563318285</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.266845780779095</v>
       </c>
       <c r="E72">
-        <v>-10.4817212267116</v>
+        <v>-8.407227283797813</v>
       </c>
       <c r="F72">
-        <v>-3.816181912549869</v>
+        <v>-5.009852713044734</v>
       </c>
       <c r="G72">
-        <v>-2.322050897368537</v>
+        <v>-2.069625110544648</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.076949196787297</v>
       </c>
       <c r="E73">
-        <v>-11.44570654567241</v>
+        <v>-8.880389418963258</v>
       </c>
       <c r="F73">
-        <v>-4.018378940266603</v>
+        <v>-4.99511274347932</v>
       </c>
       <c r="G73">
-        <v>-2.317545244889589</v>
+        <v>-1.77100066072023</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.874178325960944</v>
       </c>
       <c r="E74">
-        <v>-11.78065059717574</v>
+        <v>-8.837183248456075</v>
       </c>
       <c r="F74">
-        <v>-4.357576339262736</v>
+        <v>-5.136896108142484</v>
       </c>
       <c r="G74">
-        <v>-2.042683890946059</v>
+        <v>-1.473200536735091</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.669405290993974</v>
       </c>
       <c r="E75">
-        <v>-10.80949670386079</v>
+        <v>-9.464539923582695</v>
       </c>
       <c r="F75">
-        <v>-3.989405133618885</v>
+        <v>-5.057407628904648</v>
       </c>
       <c r="G75">
-        <v>-1.613769610878085</v>
+        <v>-1.159655458165177</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.474841022970459</v>
       </c>
       <c r="E76">
-        <v>-11.40942441192295</v>
+        <v>-9.909725146328752</v>
       </c>
       <c r="F76">
-        <v>-4.326371739199279</v>
+        <v>-5.241243893138331</v>
       </c>
       <c r="G76">
-        <v>-1.602282017856814</v>
+        <v>-0.9245007874196663</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.300640408774183</v>
       </c>
       <c r="E77">
-        <v>-11.7440242994017</v>
+        <v>-10.49205973287111</v>
       </c>
       <c r="F77">
-        <v>-4.302030991435418</v>
+        <v>-5.394746171448899</v>
       </c>
       <c r="G77">
-        <v>-1.409181207096665</v>
+        <v>-0.8293027398923841</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.15259224800048</v>
       </c>
       <c r="E78">
-        <v>-12.1857542964799</v>
+        <v>-10.27511865705966</v>
       </c>
       <c r="F78">
-        <v>-4.583186343252196</v>
+        <v>-5.286531567416783</v>
       </c>
       <c r="G78">
-        <v>-2.129678406627028</v>
+        <v>-1.484095542104832</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.032038860754382</v>
       </c>
       <c r="E79">
-        <v>-12.71626502647849</v>
+        <v>-10.97616266123909</v>
       </c>
       <c r="F79">
-        <v>-4.904577156557751</v>
+        <v>-5.593380390966193</v>
       </c>
       <c r="G79">
-        <v>-1.069737730773033</v>
+        <v>-1.084820576249952</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.935077237121496</v>
       </c>
       <c r="E80">
-        <v>-13.17571947082271</v>
+        <v>-11.16664386342373</v>
       </c>
       <c r="F80">
-        <v>-4.75665476107244</v>
+        <v>-5.638568661156309</v>
       </c>
       <c r="G80">
-        <v>-1.336190299046813</v>
+        <v>-1.163356648078083</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.855581868416356</v>
       </c>
       <c r="E81">
-        <v>-13.82379391453443</v>
+        <v>-12.18519729417696</v>
       </c>
       <c r="F81">
-        <v>-4.263721484158149</v>
+        <v>-5.462331839475908</v>
       </c>
       <c r="G81">
-        <v>-1.50949735802766</v>
+        <v>-0.9494589902402318</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.783025599005287</v>
       </c>
       <c r="E82">
-        <v>-15.74480428790625</v>
+        <v>-12.78566841912004</v>
       </c>
       <c r="F82">
-        <v>-4.561493057707682</v>
+        <v>-5.742190796307304</v>
       </c>
       <c r="G82">
-        <v>-1.41478927124019</v>
+        <v>-0.7606519570445175</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.706248455959873</v>
       </c>
       <c r="E83">
-        <v>-15.01153566268823</v>
+        <v>-13.30074610970049</v>
       </c>
       <c r="F83">
-        <v>-4.856574922300325</v>
+        <v>-5.943445141919653</v>
       </c>
       <c r="G83">
-        <v>-1.130645147604544</v>
+        <v>-0.1512070076290061</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.617952868772524</v>
       </c>
       <c r="E84">
-        <v>-15.31087685154326</v>
+        <v>-14.23882402886341</v>
       </c>
       <c r="F84">
-        <v>-5.26630614891003</v>
+        <v>-5.95622436584264</v>
       </c>
       <c r="G84">
-        <v>-1.754712776667016</v>
+        <v>-0.02421779128810265</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.515197297800552</v>
       </c>
       <c r="E85">
-        <v>-17.55398852413265</v>
+        <v>-16.11169672353369</v>
       </c>
       <c r="F85">
-        <v>-4.848824716879733</v>
+        <v>-6.091944081117312</v>
       </c>
       <c r="G85">
-        <v>-1.357434069772317</v>
+        <v>-0.2699695183048207</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.400671190606228</v>
       </c>
       <c r="E86">
-        <v>-17.79343611576223</v>
+        <v>-16.36366101732047</v>
       </c>
       <c r="F86">
-        <v>-5.184374814201339</v>
+        <v>-6.053603924246139</v>
       </c>
       <c r="G86">
-        <v>-1.223320559430902</v>
+        <v>-0.5706597485457441</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.275601754682528</v>
       </c>
       <c r="E87">
-        <v>-19.11165225702504</v>
+        <v>-18.36629713468055</v>
       </c>
       <c r="F87">
-        <v>-5.16527183352538</v>
+        <v>-5.959126136854647</v>
       </c>
       <c r="G87">
-        <v>-1.438396771480733</v>
+        <v>-0.3568945125294642</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.137975321565452</v>
       </c>
       <c r="E88">
-        <v>-20.73688082211186</v>
+        <v>-18.18066139968412</v>
       </c>
       <c r="F88">
-        <v>-4.862636914954011</v>
+        <v>-6.38653348128899</v>
       </c>
       <c r="G88">
-        <v>-0.6781332989326438</v>
+        <v>0.341590869710285</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.983099270690967</v>
       </c>
       <c r="E89">
-        <v>-23.40260327451907</v>
+        <v>-20.21297713569047</v>
       </c>
       <c r="F89">
-        <v>-5.403096114869118</v>
+        <v>-6.260096036946389</v>
       </c>
       <c r="G89">
-        <v>-1.162694538970228</v>
+        <v>-0.408188105114932</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.809022303308552</v>
       </c>
       <c r="E90">
-        <v>-23.53650119397787</v>
+        <v>-22.08195987118816</v>
       </c>
       <c r="F90">
-        <v>-5.466269069741414</v>
+        <v>-6.527077608317565</v>
       </c>
       <c r="G90">
-        <v>-1.238943023830722</v>
+        <v>-0.7584537548064414</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.622065901963703</v>
       </c>
       <c r="E91">
-        <v>-25.43985504719378</v>
+        <v>-23.59716010331061</v>
       </c>
       <c r="F91">
-        <v>-5.293694460348791</v>
+        <v>-6.141979128981207</v>
       </c>
       <c r="G91">
-        <v>-1.213412096631863</v>
+        <v>-0.5269837212461392</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.434482011786791</v>
       </c>
       <c r="E92">
-        <v>-27.03218424861488</v>
+        <v>-26.48158520791827</v>
       </c>
       <c r="F92">
-        <v>-5.567162562667589</v>
+        <v>-6.467102565803777</v>
       </c>
       <c r="G92">
-        <v>-2.016490854639346</v>
+        <v>-1.262788883350093</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.266155721491189</v>
       </c>
       <c r="E93">
-        <v>-29.56344272231234</v>
+        <v>-28.28000073295444</v>
       </c>
       <c r="F93">
-        <v>-5.428464866579853</v>
+        <v>-6.349057311618938</v>
       </c>
       <c r="G93">
-        <v>-1.792400027086079</v>
+        <v>-1.126586418773397</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.141803238763922</v>
       </c>
       <c r="E94">
-        <v>-30.74383022867769</v>
+        <v>-30.36755705914335</v>
       </c>
       <c r="F94">
-        <v>-5.113517923300676</v>
+        <v>-6.139039253068672</v>
       </c>
       <c r="G94">
-        <v>-1.934544920905766</v>
+        <v>-1.73002934912621</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.089181520040148</v>
       </c>
       <c r="E95">
-        <v>-33.3331505318645</v>
+        <v>-32.20127883178032</v>
       </c>
       <c r="F95">
-        <v>-4.893853112161108</v>
+        <v>-6.285970921140234</v>
       </c>
       <c r="G95">
-        <v>-3.635970005904339</v>
+        <v>-1.736177032192637</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.142310943575957</v>
       </c>
       <c r="E96">
-        <v>-35.99051115701655</v>
+        <v>-33.99811844786182</v>
       </c>
       <c r="F96">
-        <v>-5.585214345109395</v>
+        <v>-6.386082021054464</v>
       </c>
       <c r="G96">
-        <v>-2.960340630067718</v>
+        <v>-2.16114845252334</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.31185771430977</v>
       </c>
       <c r="E97">
-        <v>-37.44888809729076</v>
+        <v>-35.57246960747247</v>
       </c>
       <c r="F97">
-        <v>-5.139910537121271</v>
+        <v>-6.226868563685295</v>
       </c>
       <c r="G97">
-        <v>-3.132151322464814</v>
+        <v>-2.794078411994441</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.624084919992702</v>
       </c>
       <c r="E98">
-        <v>-41.16101183136138</v>
+        <v>-38.50169943391202</v>
       </c>
       <c r="F98">
-        <v>-5.185298443855461</v>
+        <v>-6.133316891050133</v>
       </c>
       <c r="G98">
-        <v>-3.873001755970617</v>
+        <v>-3.19203909127023</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.048443978259392</v>
       </c>
       <c r="E99">
-        <v>-44.09389387208811</v>
+        <v>-41.49975753679415</v>
       </c>
       <c r="F99">
-        <v>-5.738169900934116</v>
+        <v>-6.270495361321133</v>
       </c>
       <c r="G99">
-        <v>-3.655373113310008</v>
+        <v>-3.825326589659573</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.614328460809568</v>
       </c>
       <c r="E100">
-        <v>-45.20853246433609</v>
+        <v>-43.90717583180385</v>
       </c>
       <c r="F100">
-        <v>-5.398561631706194</v>
+        <v>-6.074572388313203</v>
       </c>
       <c r="G100">
-        <v>-4.598319109806159</v>
+        <v>-4.454396453031884</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.231803187027158</v>
       </c>
       <c r="E101">
-        <v>-47.87242767748121</v>
+        <v>-46.15657302631589</v>
       </c>
       <c r="F101">
-        <v>-5.085500881003191</v>
+        <v>-5.920893667745839</v>
       </c>
       <c r="G101">
-        <v>-4.464751839478724</v>
+        <v>-4.386675933480553</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.983260121121423</v>
       </c>
       <c r="E102">
-        <v>-49.80288444763303</v>
+        <v>-48.47406714871828</v>
       </c>
       <c r="F102">
-        <v>-5.064473602850528</v>
+        <v>-5.877840100352738</v>
       </c>
       <c r="G102">
-        <v>-4.88207921015925</v>
+        <v>-5.229232947043844</v>
       </c>
     </row>
   </sheetData>
